--- a/AWS-Practices/FlexPointWorks/FlexPoint-Tasks.xlsx
+++ b/AWS-Practices/FlexPointWorks/FlexPoint-Tasks.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6645a21f49718b64/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\galax\source\repos\minorselvam\CodingPractices\AWS-Practices\FlexPointWorks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FFED9743-C021-46D4-A723-F81F7CDE94C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD8489AB-2D3D-4339-9A55-61ACF1EA067A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{576D7B34-C1E7-4202-8A0B-858A4FD0BB15}"/>
   </bookViews>
@@ -411,7 +411,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -589,6 +589,12 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -804,7 +810,7 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
@@ -826,6 +832,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="1" builtinId="30" customBuiltin="1"/>
@@ -1685,61 +1692,61 @@
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="4"/>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="D34" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="E34" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="F34" s="1" t="s">
+      <c r="F34" s="9" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B35" s="4"/>
-      <c r="C35" s="1" t="s">
+      <c r="C35" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="D35" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="E35" s="1" t="s">
+      <c r="E35" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="F35" s="1" t="s">
+      <c r="F35" s="9" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B36" s="4"/>
-      <c r="C36" s="1" t="s">
+      <c r="C36" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="D36" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="E36" s="1" t="s">
+      <c r="E36" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="F36" s="1" t="s">
+      <c r="F36" s="9" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="5"/>
-      <c r="C37" s="1" t="s">
+      <c r="C37" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="D37" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="E37" s="1" t="s">
+      <c r="E37" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="F37" s="1" t="s">
+      <c r="F37" s="9" t="s">
         <v>9</v>
       </c>
     </row>
